--- a/data-start.xlsx
+++ b/data-start.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\meonske-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E8B1D3-9413-4FF6-89C2-25DB8F9FA66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E20292-E754-43D4-AA09-6D6BDBC974AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
   <si>
     <t>Company</t>
   </si>
@@ -56,12 +56,6 @@
   </si>
   <si>
     <t>Technology</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>—</t>
   </si>
   <si>
     <t>apple inc</t>
@@ -598,10 +592,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2">
         <v>182.3</v>
@@ -615,7 +609,7 @@
     </row>
     <row r="3" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -623,19 +617,17 @@
       <c r="C3" s="2">
         <v>415.2</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2">
         <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2">
         <v>152.1</v>
@@ -649,10 +641,10 @@
     </row>
     <row r="5" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2">
         <v>239.4</v>
@@ -660,13 +652,11 @@
       <c r="D5" s="2">
         <v>78.599999999999994</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -674,9 +664,7 @@
       <c r="C6" s="2">
         <v>940.5</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="D6" s="2"/>
       <c r="E6" s="2">
         <v>11.93</v>
       </c>
@@ -701,10 +689,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -716,18 +704,18 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -747,10 +735,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -770,10 +758,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -793,13 +781,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D5" s="2">
         <v>140.30000000000001</v>
@@ -816,13 +804,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2">
         <v>31.5</v>
@@ -839,13 +827,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="D7" s="2">
         <v>154.5</v>
@@ -862,13 +850,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2">
         <v>59.8</v>
@@ -885,13 +873,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="D9" s="2">
         <v>108.9</v>
@@ -908,13 +896,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2">
         <v>155.69999999999999</v>
@@ -931,13 +919,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D11" s="2">
         <v>17.2</v>
